--- a/output/2026-09-21_05_Croazia_Dubrovačko-neretvanska_Componentistica_Ventilazione_industriale.xlsx
+++ b/output/2026-09-21_05_Croazia_Dubrovačko-neretvanska_Componentistica_Ventilazione_industriale.xlsx
@@ -474,7 +474,6 @@
           <t>Klima Sistemi d.o.o.</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr"/>
       <c r="C2" t="inlineStr">
         <is>
           <t>Dubrovnik</t>
@@ -502,7 +501,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (21/09/2026)</t>
         </is>
       </c>
     </row>
@@ -532,7 +531,6 @@
           <t>+385 20 313 133 / +385 99 1905 604</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
           <t>Dealer autorizzato multi-brand (Toshiba, Mitsubishi Electric, Gree, Vaillant, Centrometal, Daikin) per vendita, montaggio, assistenza climatizzazione/ventilazione. Email non reperita con fonte certa.</t>
@@ -540,7 +538,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (21/09/2026)</t>
         </is>
       </c>
     </row>
@@ -582,7 +580,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (21/09/2026)</t>
         </is>
       </c>
     </row>
@@ -592,7 +590,6 @@
           <t>Frigo Dubrovnik d.o.o.</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr">
         <is>
           <t>Dubrovnik (Nikole Božidarevića 2)</t>
@@ -608,7 +605,6 @@
           <t>+385 98 244 040</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
           <t>Punto vendita ufficiale brand Maxon Klima (climatizzazione/ventilazione). Telefono da directory di settore, non da sito ufficiale (azienda priva di sito proprio) - da riconfermare telefonicamente.</t>
@@ -616,7 +612,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (21/09/2026)</t>
         </is>
       </c>
     </row>
@@ -626,7 +622,6 @@
           <t>Elektromehanika Korčula j.d.o.o.</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr"/>
       <c r="C6" t="inlineStr">
         <is>
           <t>Korčula</t>
@@ -654,7 +649,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (21/09/2026)</t>
         </is>
       </c>
     </row>
@@ -684,7 +679,6 @@
           <t>+385 98 825 825</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
           <t>Vendita, montaggio e manutenzione multi-brand (Daikin, Fujitsu, Hyundai, Mitsubishi, Vivax) sull'intera Dubrovačko-neretvanska županija. Indirizzo fisico ed email non reperiti pubblicamente.</t>
